--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.81.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.81.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0081.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0081.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ã€�ã€‚</t>
+          <t>L36: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 、。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | isolated marker/symbol line :: â€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]74</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]74</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L25: isolated marker/symbol line :: 74</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | isolated marker/symbol line :: â€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]74</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,24 +664,20 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: follows: ä¸€</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: the Court when by any positive rules to refuse the motion to dismiss, onâ€˜</t>
-        </is>
-      </c>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: follows: 一</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: A</t>
+          <t>L36: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 、。</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: a</t>
+          <t>L5: isolated marker/symbol line :: ‘</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -714,19 +714,19 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: follows:â€”</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L53: symbol-only separator/garbage line :: 411).</t>
-        </is>
-      </c>
-      <c r="O4" s="1" t="inlineStr"/>
+          <t>L52: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L52: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -751,7 +751,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -766,7 +766,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: B</t>
+          <t>L53: symbol-only separator/garbage line :: 411).</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -809,7 +809,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: V</t>
+          <t>L54: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -852,7 +852,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 6</t>
+          <t>L66: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -895,7 +895,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L78: symbol-only separator/garbage line :: 1850.</t>
+          <t>L67: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -938,7 +938,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: B</t>
+          <t>L78: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -979,7 +979,11 @@
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L85: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
@@ -1005,7 +1009,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1039,12 +1043,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
